--- a/構想_システム方式設計/RasberryPi受信コンポーネント_方式設計資料.xlsx
+++ b/構想_システム方式設計/RasberryPi受信コンポーネント_方式設計資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RcCarProject\構想_システム方式設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5372DCF9-1937-465A-AB71-C27CECC8A48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC5103E-5B0E-4F48-B8E9-ACBF467F3E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{22F73289-A11A-4AA9-9F84-7F03D3E15DF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{22F73289-A11A-4AA9-9F84-7F03D3E15DF9}"/>
   </bookViews>
   <sheets>
     <sheet name="はじめに" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,19 @@
     <sheet name="通信形式について" sheetId="3" r:id="rId3"/>
     <sheet name="通信イメージについて" sheetId="4" r:id="rId4"/>
     <sheet name="状態遷移について" sheetId="5" r:id="rId5"/>
+    <sheet name="CommandLayer層のイメージについて" sheetId="6" r:id="rId6"/>
+    <sheet name="ControlLogic層のイメージについて" sheetId="7" r:id="rId7"/>
+    <sheet name="DriverWrapper層のイメージについて" sheetId="8" r:id="rId8"/>
+    <sheet name="Driver層のイメージについて" sheetId="9" r:id="rId9"/>
+    <sheet name="異常系について" sheetId="10" r:id="rId10"/>
+    <sheet name="テスト戦略" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">CommandLayer層のイメージについて!$A$1:$R$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">DriverWrapper層のイメージについて!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">テスト戦略!$A$1:$O$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">はじめに!$A$1:$K$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">異常系について!$A$1:$R$120</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">状態遷移について!$A$1:$P$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">通信イメージについて!$A$1:$T$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">通信形式について!$A$1:$L$68</definedName>
@@ -44,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="220">
   <si>
     <t>はじめに</t>
     <phoneticPr fontId="1"/>
@@ -786,6 +796,1505 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandLayer層のイメージについて</t>
+    <rPh sb="12" eb="13">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandLayer層で行う責務は以下</t>
+    <rPh sb="12" eb="13">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セキム</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rawデータの正規化</t>
+    <rPh sb="7" eb="10">
+      <t>セイキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロトコルバリデーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ICommandParserによる抽象コマンドクラスの変換</t>
+    <rPh sb="17" eb="19">
+      <t>チュウショウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログ・トレース・メトリクス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例外ハンドリング</t>
+    <rPh sb="0" eb="2">
+      <t>レイガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ControlLogicのDispatch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれの言葉の意味</t>
+    <rPh sb="5" eb="7">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dispatch・・処理を適切な場所に振り分けをすること</t>
+    <rPh sb="10" eb="12">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ 正規化・・Trimとか、改行コードを統一、制御文字の排除、文字コードの統一とかをして扱いやすい形に成型すること</t>
+    <rPh sb="2" eb="5">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイギョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハイジョ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>セイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリデーション・・流れてきたデータが適切な形として渡ってきているかを判定すること</t>
+    <rPh sb="9" eb="10">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★どの粒度でそれぞれ判定を行うか</t>
+    <rPh sb="3" eb="5">
+      <t>リュウド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① 正規化処理</t>
+    <rPh sb="2" eb="5">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandLayer は受信した raw データに対して以下の正規化を行う。</t>
+  </si>
+  <si>
+    <t>前後の空白・改行の除去(trim)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改行コードを LF に統一</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> UTF-8 への文字コード統一</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 制御文字（0x00〜0x1F）の除去</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大長チェック（1024 bytes を超える場合は破棄）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 複数コマンドが含まれる場合は改行で分割</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UTF-8 BOM が存在する場合は除去</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ それが終わると正規化後の文字列を ICommandParser に渡す。</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>② プロトコルバリデーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本格的なバリデーションはControlLogic層に移譲するものとする。CommandLayer層で行うのは以下</t>
+    <rPh sb="0" eb="3">
+      <t>ホンカクテキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマンド名が存在しているものか</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区切り文字はあるか</t>
+    <rPh sb="0" eb="2">
+      <t>クギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空文字でないか</t>
+    <rPh sb="0" eb="3">
+      <t>カラモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先頭が制御文字でないか</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長さチェック</t>
+    <rPh sb="0" eb="1">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ ICommandPaserによる抽象コマンドクラスの変換</t>
+    <rPh sb="18" eb="20">
+      <t>チュウショウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Factoryデザインを用いて設計することとする。CommandLayer層で行うのは以下</t>
+    <rPh sb="12" eb="13">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマンド名抽出</t>
+    <rPh sb="4" eb="7">
+      <t>メイチュウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パラメータ抽出</t>
+    <rPh sb="5" eb="7">
+      <t>チュウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandFactoryに移譲する</t>
+    <rPh sb="15" eb="17">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④ ログ・トレース・メトリクス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロトコルログ・・通信に関するプロトコルログ</t>
+    <rPh sb="9" eb="11">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーションログ・・解析処理に関するログ</t>
+    <rPh sb="12" eb="14">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムログ・・Bluetooth通信に関するログ</t>
+    <rPh sb="17" eb="19">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤ 例外処理</t>
+    <rPh sb="2" eb="6">
+      <t>レイガイショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥ ControlLogicのDispatch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StateManager</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PermissionMatrix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PriorityManager</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 現在のRasberryPiの状態を管理する</t>
+    <rPh sb="2" eb="4">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ コマンドに対して、優先度の振り分けを行って、どの順番でRasberryPiに処理をお願いするかを決める管理をする</t>
+    <rPh sb="7" eb="8">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 現在の状態と「許可」・「拒否」の突き合わせ確認を行い、ダメならControlLogic層に流し込まないという管理をする</t>
+    <rPh sb="2" eb="4">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キョヒ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>方式としては以下のように決めることとする。基本的にはDispatcherで確認を行うという形で決める</t>
+    <rPh sb="0" eb="2">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構造のイメージ</t>
+    <rPh sb="0" eb="2">
+      <t>コウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandParserの抽象クラスとする</t>
+    <rPh sb="14" eb="16">
+      <t>チュウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリデーションを行う</t>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規化処理を行う</t>
+    <rPh sb="0" eb="3">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマンドについて辞書管理しておく</t>
+    <rPh sb="8" eb="12">
+      <t>ジショカンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際にコマンドを生成する</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態管理・優先度管理・例外処理管理を行う</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウタイカンリ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>レイガイショリ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信マトリクスを用いて、あらかじめ条件に合致しない通信は弾いておく</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガッチ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ControlLogic層のイメージについて</t>
+    <rPh sb="12" eb="13">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>抽象コマンドを具体的な物理操作に変更する</t>
+    <rPh sb="0" eb="2">
+      <t>チュウショウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>センサ値を用いてフィードバック制御を行う</t>
+    <rPh sb="3" eb="4">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ControlLogic層では以下の責務を行うものとする</t>
+    <rPh sb="12" eb="13">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セキム</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MoveExecutor()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TurnExecutor()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StopExecutor()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SafetyExecutor()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandExecutorクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 実現例</t>
+    <rPh sb="2" eb="5">
+      <t>ジツゲンレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FeedbackControllerクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AngleFeedback()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TemperatureFeedBack()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BatteryFeedBack()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ コントローラーのコマンドに応じた制御Executorを作成すること</t>
+    <rPh sb="15" eb="16">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ センサの値に応じてフィードバック制御を入れること</t>
+    <rPh sb="6" eb="7">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ あくまでも採取した値に応じてイベントを投げるだけ</t>
+  </si>
+  <si>
+    <t>本格的なバリデーション処理もここで行う</t>
+    <rPh sb="0" eb="3">
+      <t>ホンカクテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DriverWrapper層のイメージについて</t>
+    <rPh sb="13" eb="14">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DriverWrapper層の行うことは以下</t>
+    <rPh sb="13" eb="14">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 実際に物理的なGPIO番号やI2Cアドレスを隠蔽するようにするのが目的</t>
+    <rPh sb="2" eb="4">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>インペイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あとは、実際に受け渡ってきたCommandをParseして物理処理へと変換する。</t>
+    <rPh sb="4" eb="6">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それと、閾値チェックなのでValidationもWrapperで行うものとする</t>
+    <rPh sb="4" eb="6">
+      <t>シキイチ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層のイメージについて</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常系について</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト戦略</t>
+    <rPh sb="3" eb="5">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>具体的には、以下のような処理を作成するイメージとする。</t>
+    <rPh sb="0" eb="3">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前提・・上位層から、Commandが流れてくる</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ex. moveForward()、moveBack()など</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これらを、Driver層のメソッドの組み合わせとして呼び出すのが責務とする。</t>
+    <rPh sb="11" eb="12">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セキム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ 一番上層は抽象化クラスとする</t>
+    <rPh sb="2" eb="4">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウソウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>チュウショウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ MotorDriverWrapper</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この部分での実現事項は以下</t>
+    <rPh sb="2" eb="4">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SensorDriverWrapper</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BatteryDriverWrapper</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モータ制御の抽象化</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>チュウショウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>センサ制御の抽象化</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>チュウショウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッテリー制御の抽象化</t>
+    <rPh sb="5" eb="7">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>チュウショウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層では、以下のような責務を持つこととする</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セキム</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① GPIO制御</t>
+    <rPh sb="6" eb="8">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>② PWM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ I2C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④ SPI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤ UART</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電気制御</t>
+    <rPh sb="0" eb="2">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モータ制御</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低速デジタル通信制御</t>
+    <rPh sb="0" eb="2">
+      <t>テイソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高速デジタル通信制御</t>
+    <rPh sb="0" eb="2">
+      <t>コウソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シリアル通信制御</t>
+    <rPh sb="4" eb="6">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ Bluetooth通信(SPPプロファイル)で通信を行う場合は、UART通信を行えばつながる</t>
+    <rPh sb="11" eb="13">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層のクラスイメージは以下とする</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本章での開発スコープ</t>
+    <rPh sb="0" eb="2">
+      <t>ホンショウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発スコープ外</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本章での開発スコープ外</t>
+    <rPh sb="0" eb="2">
+      <t>ホンショウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ クラス・メソッド例</t>
+    <rPh sb="10" eb="11">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpioInterface()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PwmInterface()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2cInterface()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpiInterface()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UartInterface()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電気制御系IF</t>
+    <rPh sb="0" eb="4">
+      <t>デンキセイギョ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モータ制御系IF</t>
+    <rPh sb="3" eb="6">
+      <t>セイギョケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低速デジタル通信系IF</t>
+    <rPh sb="0" eb="2">
+      <t>テイソク</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ツウシンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高速デジタル通信系IF</t>
+    <rPh sb="0" eb="2">
+      <t>コウソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シリアル通信IF</t>
+    <rPh sb="4" eb="6">
+      <t>ツウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ ジャイロセンサとか、加速度センサとかを用いるときに使う。拡張性を考えてIFだけ用意</t>
+    <rPh sb="12" eb="15">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>カクチョウセイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 走行ログをSDカードに保存するときに使う。こちらは必要か</t>
+    <rPh sb="2" eb="4">
+      <t>ソウコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ 具体的な使用例</t>
+    <rPh sb="2" eb="5">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>シヨウレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ モータを動かすときに使う。必須</t>
+    <rPh sb="6" eb="7">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 電気系統を制御する際に使う。必須</t>
+    <rPh sb="2" eb="6">
+      <t>デンキケイトウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MotorRawDriver()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SensorRawDriver()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BatteryRawDriver()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>方式設計断面で考える異常系としては以下を考えるものとする</t>
+    <rPh sb="0" eb="2">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダンメン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① バッテリー電圧低下</t>
+    <rPh sb="7" eb="9">
+      <t>デンアツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>② 電流不足</t>
+    <rPh sb="2" eb="6">
+      <t>デンリュウブソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ ケーブル抜け</t>
+    <rPh sb="6" eb="7">
+      <t>ヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④ モータの故障</t>
+    <rPh sb="6" eb="8">
+      <t>コショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤ センサの故障</t>
+    <rPh sb="6" eb="8">
+      <t>コショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥ 温度上昇</t>
+    <rPh sb="2" eb="6">
+      <t>オンドジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HW異常</t>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モータが動かなくなる</t>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RasberryPiが再起動する</t>
+    <rPh sb="11" eb="14">
+      <t>サイキドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPIOが反応しない</t>
+    <rPh sb="5" eb="7">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PWMを送っても反応しない</t>
+    <rPh sb="4" eb="5">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2C/SPI応答無</t>
+    <rPh sb="7" eb="9">
+      <t>オウトウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RasberryPiのスロットリング(性能低下)</t>
+    <rPh sb="19" eb="21">
+      <t>セイノウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層異常</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信異常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPIO・PWM・I2C・SPIの制御異常</t>
+    <rPh sb="17" eb="19">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OS・プロセス異常</t>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層でのハンドリング</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CommandLayer層～DriverWrapper層は</t>
+    <rPh sb="12" eb="13">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pytestで自動デバッグを行う</t>
+    <rPh sb="7" eb="9">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Driver層は実機デバッグを行う</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -794,7 +2303,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,8 +2354,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -865,6 +2383,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -880,7 +2404,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -900,6 +2424,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1509,6 +3045,733 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="雲 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{085A2260-EF3A-4E62-A4CF-0559A7A087A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2659380" y="617220"/>
+          <a:ext cx="2727960" cy="1188720"/>
+        </a:xfrm>
+        <a:prstGeom prst="cloud">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>Android</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>Controller</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>※ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1"/>
+            <a:t>別紙参照</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3170BF1B-ABC7-4D08-88B9-BBDA24A17CFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2697480" y="2598420"/>
+          <a:ext cx="2667000" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+            <a:t>CommandLayer</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{610EAACA-6A67-4799-9278-97490CC6CEAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2697480" y="4267200"/>
+          <a:ext cx="2667000" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+            <a:t>ControllLogic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723F7D3E-588F-48ED-A753-1BD32F24A729}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2697480" y="7924800"/>
+          <a:ext cx="2667000" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+            <a:t>Driver</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E36C50EF-DF56-43B6-AD93-003318620B00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2689860" y="6080760"/>
+          <a:ext cx="2667000" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+            <a:t>DriverWrapper</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>67314</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CFB5316-84DB-4B5B-99B3-75580798E209}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="1"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4023360" y="1804674"/>
+          <a:ext cx="7620" cy="793746"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3F0BE4-F5AF-4B2B-A6A6-D00A891B040F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4030980" y="3505200"/>
+          <a:ext cx="0" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3021571-A60E-47D0-8D07-8C8DFCB4809D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4023360" y="5181600"/>
+          <a:ext cx="7620" cy="899160"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2C6AE5F-999B-447B-A750-732755125619}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4023360" y="6995160"/>
+          <a:ext cx="7620" cy="929640"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2ADA493-9601-22CD-0440-FB05A1CC1446}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2316480" y="2369820"/>
+          <a:ext cx="3497580" cy="4777740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDCB795-4B80-4380-9C17-099C05B9C116}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2308860" y="7589520"/>
+          <a:ext cx="3497580" cy="1478280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3595,6 +5858,1687 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69628493-B923-D08B-F43A-62410CED90C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2026920" y="11551920"/>
+          <a:ext cx="2171700" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>IF</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5927</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>227753</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>165947</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>220133</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7619A561-DA4A-40F0-9F9B-A7D9ECEEC600}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2012527" y="21140420"/>
+          <a:ext cx="2166620" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>CommamdParser</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9313</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>14393</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>169333</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>6773</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C0AF475-4C6F-4537-B13C-A4642764AAE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2015913" y="22527260"/>
+          <a:ext cx="2166620" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>CommamdFactory</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>10160</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>14393</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>170180</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>6773</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C32648F-B422-4D79-A677-FCDBD5A6E643}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2016760" y="23898860"/>
+          <a:ext cx="2166620" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>CommamdDifinition</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>655321</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>251461</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>184161</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E6EEE72-A29D-492B-23A9-496AB0E3F96A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1325881" y="12938760"/>
+          <a:ext cx="4960620" cy="2668281"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>61262</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>221394</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45E761EB-266A-C1B6-5C17-B6E054ECAF66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6637020" y="12923520"/>
+          <a:ext cx="3482642" cy="4778154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>667173</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>11005</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>158326</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>3385</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5FC5CA0-CA10-4E47-BE82-C6E33C708466}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2004906" y="25267072"/>
+          <a:ext cx="2166620" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>CommamdDispatcher</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07051031-DFC2-7EDB-8BB7-8145148CFDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2689860" y="4716780"/>
+          <a:ext cx="2011680" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>ControlLogic</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A5CF13F-2E5F-416A-A875-8945DC1A5858}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670560" y="6103620"/>
+          <a:ext cx="2011680" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>CommandExecutor</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6341E3F6-74EF-4FB2-92CE-9725AD842AC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4716780" y="6080760"/>
+          <a:ext cx="2011680" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
+            <a:t>FeedbackController</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6AB28E-3501-FBB9-3589-43A858960507}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1676400" y="5410200"/>
+          <a:ext cx="2019300" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E953678-AB44-45C2-A6C9-F98F9EB36640}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3695700" y="5410200"/>
+          <a:ext cx="2026920" cy="670560"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3964B161-E0A6-4D14-A774-4BAEBAABC674}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="15" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1668780" y="6797040"/>
+          <a:ext cx="7620" cy="1112520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B6ED469-C61A-48AB-BF84-374B6EA41B83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="7909560"/>
+          <a:ext cx="2011680" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>DriverFacade</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>215357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12958</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36DF65E4-FD24-42E9-5C3F-43C20CB8CE17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="809717"/>
+          <a:ext cx="5113020" cy="3226601"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A581D8-9AE5-F807-92FD-502980F1D50E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1348740" y="5615940"/>
+          <a:ext cx="2270760" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1"/>
+            <a:t>DriverFacade</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C71DD35-770C-E574-EB05-AA417F42C35D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2484120" y="6309360"/>
+          <a:ext cx="7620" cy="929640"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E621123-9CEE-4D2B-85A9-C3ED16FA156C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1356360" y="7239000"/>
+          <a:ext cx="2270760" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+            <a:t>DriverWrapper</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CAF5876-71A7-2B3F-157C-B34308C1B938}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2026920" y="4008120"/>
+          <a:ext cx="1996440" cy="716280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>DriverWrapper</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0709C656-5BC8-9BD3-AE20-80D92509162E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3025140" y="4724400"/>
+          <a:ext cx="0" cy="922020"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA8ABFE3-E079-2D13-CA3E-29C853F9327A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2026920" y="5646420"/>
+          <a:ext cx="1996440" cy="1120140"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>HardwareIF</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A76FE111-B8EF-4B94-BB9D-30199A639783}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="2"/>
+          <a:endCxn id="12" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3025140" y="6766560"/>
+          <a:ext cx="0" cy="922020"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40ACDB73-DF30-472C-A0C4-ECEC4DD01E70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2026920" y="7688580"/>
+          <a:ext cx="1996440" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>DeviceRawDriver</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>411748</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160192</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC20D184-B407-58E6-4620-B9F9F1CF4690}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="3108960"/>
+          <a:ext cx="3093988" cy="1988992"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>587140</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>137628</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4533DA3B-A677-3B5E-F4D1-FF71AC01BA42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="5623560"/>
+          <a:ext cx="4610500" cy="5395428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>312854</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>91805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDF4CF8E-215B-5E2E-33B2-AAE6120C3C9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="11795760"/>
+          <a:ext cx="5006774" cy="4206605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>587081</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>198553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7C08BD9-2A27-F1B7-23C8-9D13CCE5A511}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7376160" y="11795760"/>
+          <a:ext cx="3939881" cy="4999153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114717</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>46120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{895FBA00-A3AB-CCFC-CF2C-C2E745086EE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="17739360"/>
+          <a:ext cx="4808637" cy="4618120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>472887</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>122287</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0196349F-ED21-77AA-A13D-1754509C76EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1348740" y="23225760"/>
+          <a:ext cx="5159187" cy="4237087"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3922,6 +7866,224 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270AFA1-A0D0-4515-BFA4-DA3457E82438}">
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B77" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B78" s="2"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B101" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="32" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F361FA7-1377-438B-AD70-EA52BF09B220}">
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="19" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+    </row>
+    <row r="22" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="23" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+    </row>
+    <row r="27" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="33" spans="10:13" x14ac:dyDescent="0.45">
+      <c r="J33" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="10:13" x14ac:dyDescent="0.45">
+      <c r="J35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="10:13" x14ac:dyDescent="0.45">
+      <c r="J36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="10:13" x14ac:dyDescent="0.45">
+      <c r="J37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="50" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C481514-91AC-4BFE-A2AC-25B376AF916D}">
   <dimension ref="A1:Q37"/>
@@ -4332,4 +8494,814 @@
   <pageSetup paperSize="9" scale="50" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC511A0-3104-4A31-97C9-4A896E2CBC38}">
+  <dimension ref="A1:H112"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C5" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C8" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C9" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C10" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="C19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D30" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C33" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D34" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D36" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D37" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D38" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D39" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D40" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C43" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D44" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D46" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D47" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D48" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D51" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D52" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D53" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C80" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C82" s="2"/>
+      <c r="D82" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C83" s="2"/>
+      <c r="D83" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="86" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C86" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="H87" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="H93" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="94" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="H94" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H99" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H105" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="111" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H111" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H112" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="33" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0E9CB2-480A-420C-AB50-C97E8E36FAA6}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C15" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C16" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C17" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B21" s="8"/>
+      <c r="C21" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B22" s="9"/>
+      <c r="C22" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9874818A-673F-4F90-BFA4-C434BAF4C04C}">
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J4" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J5" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J6" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C23" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G25" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G32" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G34" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G35" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="53" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702F4456-2AE6-48A0-81B7-842324D6DBC3}">
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="2"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="8:13" x14ac:dyDescent="0.45">
+      <c r="H29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H34" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H35" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H36" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="41" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>